--- a/Common Header (2).xlsx
+++ b/Common Header (2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pramitab\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janarddanm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5788E3-20F8-4715-8174-D5B171D8BB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9232C9A0-0A7C-4C65-85D6-3F10D58F9D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B867CAC2-6045-47E5-8C7C-5A68980B1552}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B867CAC2-6045-47E5-8C7C-5A68980B1552}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
   <si>
     <t>STATE</t>
   </si>
@@ -89,39 +89,15 @@
     <t>RELEASE DATE</t>
   </si>
   <si>
-    <t>CITY OF MOUNTAIN VIEW</t>
-  </si>
-  <si>
-    <t>CHEROKEE COUNTY</t>
-  </si>
-  <si>
     <t>CA</t>
   </si>
   <si>
     <t>LG</t>
   </si>
   <si>
-    <t>CIT</t>
-  </si>
-  <si>
     <t>CNT</t>
   </si>
   <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>ESG</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>JJZLKAS3G111</t>
-  </si>
-  <si>
-    <t>DCEGK6HA11M5</t>
-  </si>
-  <si>
     <t>URL 1 [PRIOR YEAR PDF LINK]</t>
   </si>
   <si>
@@ -131,22 +107,166 @@
     <t>URL 3 [CURRENT YEAR XBRL LINK]</t>
   </si>
   <si>
-    <t>ADANI ENTERPRISES LIMITED</t>
-  </si>
-  <si>
-    <t>CARE Ratings Limited</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com/corporate/CARERATINGS_17062025213045_BRSRAREXTRACT.pdf</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com/corporate/xbrl/BRSR_1467766_17062025093057_WEB.xml</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com/corporate/xbrl/BRSR_1468306_18062025105504_WEB.xml</t>
-  </si>
-  <si>
-    <t>https://nsearchives.nseindia.com/corporate/nishant_joshi_adani_com_18062025225251_AELIntimationforsubmissionofBRSR.pdf</t>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>OSD</t>
+  </si>
+  <si>
+    <t>LOCUST VALLEY CENTRAL SCHOOL DISTRICT (NASSAU COUNTY)</t>
+  </si>
+  <si>
+    <t>GENESEE VALLEY CENTRAL SCHOOL DISTRICT</t>
+  </si>
+  <si>
+    <t>ATTICA CENTRAL SCHOOL DISTRICT (WYOMING COUNTY)</t>
+  </si>
+  <si>
+    <t>HARRISON CENTRAL SCHOOL DISTRICT (WESTCHESTER COUNTY)</t>
+  </si>
+  <si>
+    <t>VALLEY STREAM UNION FREE SCHOOL DISTRICT #24</t>
+  </si>
+  <si>
+    <t>DOVER UNION FREE SCHOOL DISTRICT (DUTCHESS COUNTY)</t>
+  </si>
+  <si>
+    <t>LITTLE FALLS CITY SCHOOL DISTRICT (HERKIMER COUNTY)</t>
+  </si>
+  <si>
+    <t>COMMUNITY ACTION PARTNERSHIP OF SAN LUIS OBISPO COUNTY, INC.</t>
+  </si>
+  <si>
+    <t>SALAMANCA CITY CENTRAL SCHOOL DISTRICT</t>
+  </si>
+  <si>
+    <t>LIVINGSTON MANOR CENTRAL SCHOOL DISTRICT (SULLIVAN COUNTY)</t>
+  </si>
+  <si>
+    <t>SULLIVAN WEST CENTRAL SCHOOL DISTRICT</t>
+  </si>
+  <si>
+    <t>CHEEKTOWAGA-SLOAN UNION FREE SCHOOL DISTRICT (ERIE COUNTY)</t>
+  </si>
+  <si>
+    <t>SHENENDEHOWA CENTRAL SCHOOL DISTRICT AT CLIFTON PARK, NEW YORK</t>
+  </si>
+  <si>
+    <t>HERMON-DEKALB CENTRAL SCHOOL DISTRICT</t>
+  </si>
+  <si>
+    <t>SARATOGA SPRINGS CITY SCHOOL DISTRICT (SARATOGA COUNTY)</t>
+  </si>
+  <si>
+    <t>WASHINGTONVILLE CENTRAL SCHOOL DISTRICT (ORANGE COUNTY)</t>
+  </si>
+  <si>
+    <t>SPECIAL SCHOOL DISTRICT NO. 6</t>
+  </si>
+  <si>
+    <t>NORTHERN ADIRONDACK CENTRAL SCHOOL</t>
+  </si>
+  <si>
+    <t>LAC QUI PARLE VALLEY ISD #2853</t>
+  </si>
+  <si>
+    <t>ENLARGED CITY SCHOOL DISTRICT OF THE CITY OF AMSTERDAM</t>
+  </si>
+  <si>
+    <t>HAVERSTRAW-STONY POINT CENTRAL SCHOOL DISTRICT</t>
+  </si>
+  <si>
+    <t>SONOMA COUNTY COMMUNITY DEVELOPMENT COMMISON</t>
+  </si>
+  <si>
+    <t>VERNON VERONA SHERRILL CENTRAL SCHOOL DISTRICT</t>
+  </si>
+  <si>
+    <t>LAGUNA BEACH UNIFIED SCHOOL DISTRICT</t>
+  </si>
+  <si>
+    <t>STANISLAUS COUNTY AFFORDABLE HOUSING, INC.</t>
+  </si>
+  <si>
+    <t>UJNMLRMMXZE3</t>
+  </si>
+  <si>
+    <t>Y74QNCRL7TU1</t>
+  </si>
+  <si>
+    <t>PM9KRR8JV796</t>
+  </si>
+  <si>
+    <t>MNXPQFJ5GN71</t>
+  </si>
+  <si>
+    <t>JGN4A16GM9T5</t>
+  </si>
+  <si>
+    <t>UBJQGQ7HDK66</t>
+  </si>
+  <si>
+    <t>TJYGVL26ZKA5</t>
+  </si>
+  <si>
+    <t>GBL8FWWVCLC5</t>
+  </si>
+  <si>
+    <t>UBN7JRQVEAJ9</t>
+  </si>
+  <si>
+    <t>P6L2Z5GMB964</t>
+  </si>
+  <si>
+    <t>S6G7YR4BN3C8</t>
+  </si>
+  <si>
+    <t>NCCCMFJB61G5</t>
+  </si>
+  <si>
+    <t>GU9NJ5MK5867</t>
+  </si>
+  <si>
+    <t>KK2JKV1KMPX5</t>
+  </si>
+  <si>
+    <t>Z3HSGDXBXT61</t>
+  </si>
+  <si>
+    <t>MYZZKB8USRT3</t>
+  </si>
+  <si>
+    <t>LXH6HYN5NHG6</t>
+  </si>
+  <si>
+    <t>M5AZXK9C1S33</t>
+  </si>
+  <si>
+    <t>JL4MJBKAWN69</t>
+  </si>
+  <si>
+    <t>XBJYHF3DNTV7</t>
+  </si>
+  <si>
+    <t>YLS6WJ6DCZX3</t>
+  </si>
+  <si>
+    <t>QJKVLDMEA4B1</t>
+  </si>
+  <si>
+    <t>XYSFB36DGWK9</t>
+  </si>
+  <si>
+    <t>K4XEKH6YZKZ5</t>
+  </si>
+  <si>
+    <t>US2PW97AYKM5</t>
   </si>
 </sst>
 </file>
@@ -157,7 +277,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="mmm/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,8 +293,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,6 +316,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB5E6F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -252,6 +384,12 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -593,26 +731,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9611CE-8714-4C62-B381-8903EB736C06}">
-  <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.90625" style="2"/>
-    <col min="4" max="4" width="54.1796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" style="2"/>
-    <col min="6" max="7" width="19.1796875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="12.08984375" style="2" customWidth="1"/>
-    <col min="10" max="12" width="20.54296875" style="1" customWidth="1"/>
-    <col min="13" max="14" width="13.81640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.81640625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.81640625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.54296875" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="3" width="8.88671875" style="2"/>
+    <col min="4" max="4" width="54.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="2"/>
+    <col min="6" max="7" width="19.21875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="12.109375" style="2" customWidth="1"/>
+    <col min="10" max="12" width="20.5546875" style="1" customWidth="1"/>
+    <col min="13" max="14" width="13.77734375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.77734375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.77734375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.5546875" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -641,13 +779,13 @@
         <v>5</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>15</v>
@@ -671,28 +809,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3">
-        <v>2025</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="3">
-        <v>946000379</v>
-      </c>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="9"/>
@@ -706,28 +840,24 @@
       <c r="R2" s="7"/>
       <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3">
-        <v>566000285</v>
-      </c>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="9"/>
@@ -741,34 +871,30 @@
       <c r="R3" s="7"/>
       <c r="S3" s="4"/>
     </row>
-    <row r="4" spans="1:19" ht="87" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F4" s="3"/>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="7">
-        <v>45826</v>
-      </c>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="O4" s="4"/>
       <c r="P4" s="7"/>
@@ -776,34 +902,30 @@
       <c r="R4" s="7"/>
       <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="1:19" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F5" s="3"/>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="7">
-        <v>45825</v>
-      </c>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="4"/>
       <c r="P5" s="7"/>
@@ -811,11 +933,679 @@
       <c r="R5" s="7"/>
       <c r="S5" s="4"/>
     </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="4"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="4"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="4"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="4"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="4"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="4"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="4"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="4"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="4"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="4"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="4"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="4"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="4"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="4"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="4"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="4"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="4"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="4"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="4"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="4"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="4"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="4"/>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="K4" r:id="rId1" xr:uid="{CFBC55FC-3875-4962-B045-7B1629418A9E}"/>
-    <hyperlink ref="L4" r:id="rId2" xr:uid="{6ABF1BA4-F476-49BE-B47A-35E9AE8931FD}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>